--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/6782-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/6782-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FBB285C-050F-4E78-BE35-8C28685923B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{258317A6-A1EB-472B-8A2B-E0D547D88524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{9FAD0E1A-BA23-450B-A32A-45CF1DEE6CB0}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{CC229294-BF95-4D32-BA22-7F7C61861A75}"/>
   </bookViews>
   <sheets>
     <sheet name="6782-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1481,18 +1481,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66863E44-3973-4171-B45B-7A86CF7760C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72369162-9E02-41DC-ADF6-C54A31CFF5AF}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1646,7 +1646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2025</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2.92</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2024</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>2023</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2022</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>25</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>25</v>
       </c>
@@ -2700,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2021</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>25</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>25</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2020</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39" t="s">
         <v>46</v>
       </c>
